--- a/AAAGameData/DataTables/CharacterMainPropertyTable.xlsx
+++ b/AAAGameData/DataTables/CharacterMainPropertyTable.xlsx
@@ -1,10 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="29100" windowHeight="13420"/>
+    <workbookView windowWidth="28800" windowHeight="12255"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet 1" sheetId="1" r:id="rId1"/>
@@ -94,10 +94,10 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
   <numFmts count="4">
-    <numFmt numFmtId="42" formatCode="_(&quot;$&quot;* #,##0_);_(&quot;$&quot;* \(#,##0\);_(&quot;$&quot;* &quot;-&quot;_);_(@_)"/>
-    <numFmt numFmtId="44" formatCode="_(&quot;$&quot;* #,##0.00_);_(&quot;$&quot;* \(#,##0.00\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
-    <numFmt numFmtId="176" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="176" formatCode="_(&quot;$&quot;* #,##0.00_);_(&quot;$&quot;* \(#,##0.00\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="177" formatCode="_(&quot;$&quot;* #,##0_);_(&quot;$&quot;* \(#,##0\);_(&quot;$&quot;* &quot;-&quot;_);_(@_)"/>
   </numFmts>
   <fonts count="22">
     <font>
@@ -114,7 +114,7 @@
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
+      <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -122,7 +122,7 @@
       <u/>
       <sz val="11"/>
       <color rgb="FF0000FF"/>
-      <name val="Calibri"/>
+      <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
@@ -130,14 +130,14 @@
       <u/>
       <sz val="11"/>
       <color rgb="FF800080"/>
-      <name val="Calibri"/>
+      <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FFFF0000"/>
-      <name val="Calibri"/>
+      <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
@@ -145,7 +145,7 @@
       <b/>
       <sz val="18"/>
       <color theme="3"/>
-      <name val="Calibri"/>
+      <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -153,7 +153,7 @@
       <i/>
       <sz val="11"/>
       <color rgb="FF7F7F7F"/>
-      <name val="Calibri"/>
+      <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
@@ -161,7 +161,7 @@
       <b/>
       <sz val="15"/>
       <color theme="3"/>
-      <name val="Calibri"/>
+      <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -169,7 +169,7 @@
       <b/>
       <sz val="13"/>
       <color theme="3"/>
-      <name val="Calibri"/>
+      <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -177,14 +177,14 @@
       <b/>
       <sz val="11"/>
       <color theme="3"/>
-      <name val="Calibri"/>
+      <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF3F3F76"/>
-      <name val="Calibri"/>
+      <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
@@ -192,7 +192,7 @@
       <b/>
       <sz val="11"/>
       <color rgb="FF3F3F3F"/>
-      <name val="Calibri"/>
+      <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
@@ -200,7 +200,7 @@
       <b/>
       <sz val="11"/>
       <color rgb="FFFA7D00"/>
-      <name val="Calibri"/>
+      <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
@@ -208,14 +208,14 @@
       <b/>
       <sz val="11"/>
       <color rgb="FFFFFFFF"/>
-      <name val="Calibri"/>
+      <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FFFA7D00"/>
-      <name val="Calibri"/>
+      <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
@@ -223,42 +223,42 @@
       <b/>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
+      <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF006100"/>
-      <name val="Calibri"/>
+      <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF9C0006"/>
-      <name val="Calibri"/>
+      <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF9C6500"/>
-      <name val="Calibri"/>
+      <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color theme="0"/>
-      <name val="Calibri"/>
+      <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
+      <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
@@ -566,19 +566,19 @@
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFill="0" applyBorder="0"/>
+    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="176" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="44" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="9" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="41" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="177" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -719,55 +719,55 @@
     </xf>
   </cellXfs>
   <cellStyles count="49">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Comma" xfId="1" builtinId="3"/>
-    <cellStyle name="Currency" xfId="2" builtinId="4"/>
-    <cellStyle name="Percent" xfId="3" builtinId="5"/>
-    <cellStyle name="Comma [0]" xfId="4" builtinId="6"/>
-    <cellStyle name="Currency [0]" xfId="5" builtinId="7"/>
-    <cellStyle name="Hyperlink" xfId="6" builtinId="8"/>
-    <cellStyle name="Followed Hyperlink" xfId="7" builtinId="9"/>
-    <cellStyle name="Note" xfId="8" builtinId="10"/>
-    <cellStyle name="Warning Text" xfId="9" builtinId="11"/>
-    <cellStyle name="Title" xfId="10" builtinId="15"/>
-    <cellStyle name="CExplanatory Text" xfId="11" builtinId="53"/>
-    <cellStyle name="Heading 1" xfId="12" builtinId="16"/>
-    <cellStyle name="Heading 2" xfId="13" builtinId="17"/>
-    <cellStyle name="Heading 3" xfId="14" builtinId="18"/>
-    <cellStyle name="Heading 4" xfId="15" builtinId="19"/>
-    <cellStyle name="Input" xfId="16" builtinId="20"/>
-    <cellStyle name="Output" xfId="17" builtinId="21"/>
-    <cellStyle name="Calculation" xfId="18" builtinId="22"/>
-    <cellStyle name="Check Cell" xfId="19" builtinId="23"/>
-    <cellStyle name="Linked Cell" xfId="20" builtinId="24"/>
-    <cellStyle name="Total" xfId="21" builtinId="25"/>
-    <cellStyle name="Good" xfId="22" builtinId="26"/>
-    <cellStyle name="Bad" xfId="23" builtinId="27"/>
-    <cellStyle name="Neutral" xfId="24" builtinId="28"/>
-    <cellStyle name="Accent1" xfId="25" builtinId="29"/>
-    <cellStyle name="20% - Accent1" xfId="26" builtinId="30"/>
-    <cellStyle name="40% - Accent1" xfId="27" builtinId="31"/>
-    <cellStyle name="60% - Accent1" xfId="28" builtinId="32"/>
-    <cellStyle name="Accent2" xfId="29" builtinId="33"/>
-    <cellStyle name="20% - Accent2" xfId="30" builtinId="34"/>
-    <cellStyle name="40% - Accent2" xfId="31" builtinId="35"/>
-    <cellStyle name="60% - Accent2" xfId="32" builtinId="36"/>
-    <cellStyle name="Accent3" xfId="33" builtinId="37"/>
-    <cellStyle name="20% - Accent3" xfId="34" builtinId="38"/>
-    <cellStyle name="40% - Accent3" xfId="35" builtinId="39"/>
-    <cellStyle name="60% - Accent3" xfId="36" builtinId="40"/>
-    <cellStyle name="Accent4" xfId="37" builtinId="41"/>
-    <cellStyle name="20% - Accent4" xfId="38" builtinId="42"/>
-    <cellStyle name="40% - Accent4" xfId="39" builtinId="43"/>
-    <cellStyle name="60% - Accent4" xfId="40" builtinId="44"/>
-    <cellStyle name="Accent5" xfId="41" builtinId="45"/>
-    <cellStyle name="20% - Accent5" xfId="42" builtinId="46"/>
-    <cellStyle name="40% - Accent5" xfId="43" builtinId="47"/>
-    <cellStyle name="60% - Accent5" xfId="44" builtinId="48"/>
-    <cellStyle name="Accent6" xfId="45" builtinId="49"/>
-    <cellStyle name="20% - Accent6" xfId="46" builtinId="50"/>
-    <cellStyle name="40% - Accent6" xfId="47" builtinId="51"/>
-    <cellStyle name="60% - Accent6" xfId="48" builtinId="52"/>
+    <cellStyle name="常规" xfId="0" builtinId="0"/>
+    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
+    <cellStyle name="货币" xfId="2" builtinId="4"/>
+    <cellStyle name="百分比" xfId="3" builtinId="5"/>
+    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
+    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
+    <cellStyle name="超链接" xfId="6" builtinId="8"/>
+    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
+    <cellStyle name="注释" xfId="8" builtinId="10"/>
+    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
+    <cellStyle name="标题" xfId="10" builtinId="15"/>
+    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
+    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
+    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
+    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
+    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
+    <cellStyle name="输入" xfId="16" builtinId="20"/>
+    <cellStyle name="输出" xfId="17" builtinId="21"/>
+    <cellStyle name="计算" xfId="18" builtinId="22"/>
+    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
+    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
+    <cellStyle name="汇总" xfId="21" builtinId="25"/>
+    <cellStyle name="好" xfId="22" builtinId="26"/>
+    <cellStyle name="差" xfId="23" builtinId="27"/>
+    <cellStyle name="适中" xfId="24" builtinId="28"/>
+    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
+    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
+    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
+    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
+    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
+    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
+    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
+    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
+    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
+    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
+    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
+    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
+    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
+    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
+    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
+    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
+    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
+    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
+    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
+    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
+    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
+    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
+    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
+    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
   </cellStyles>
   <dxfs count="17">
     <dxf>
@@ -1251,13 +1251,13 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:K9"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.8"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
-    <col min="4" max="4" width="16.5390625" customWidth="1"/>
-    <col min="5" max="11" width="16.7890625" customWidth="1"/>
+    <col min="4" max="4" width="16.5428571428571" customWidth="1"/>
+    <col min="5" max="11" width="16.7904761904762" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2">
+    <row r="1" spans="1:11">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1329,7 +1329,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="4" spans="1:4">
+    <row r="4" spans="1:11">
       <c r="A4" t="s">
         <v>0</v>
       </c>
@@ -1340,7 +1340,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="5" spans="2:11">
+    <row r="5" spans="1:11">
       <c r="B5" s="1">
         <v>1</v>
       </c>
@@ -1369,7 +1369,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="6" spans="2:11">
+    <row r="6" spans="1:11">
       <c r="B6" s="1">
         <v>2</v>
       </c>
@@ -1398,7 +1398,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="7" spans="2:11">
+    <row r="7" spans="1:11">
       <c r="B7" s="1">
         <v>3</v>
       </c>
@@ -1427,7 +1427,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="8" spans="2:11">
+    <row r="8" spans="1:11">
       <c r="B8" s="1">
         <v>4</v>
       </c>
@@ -1456,7 +1456,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="9" spans="2:11">
+    <row r="9" spans="1:11">
       <c r="B9" s="1">
         <v>5</v>
       </c>
@@ -1490,7 +1490,7 @@
     <dataValidation type="list" allowBlank="1" sqref="D1:Z1">
       <formula1>"i18n"</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="D3 E3:K3 L3:Z3">
+    <dataValidation type="list" sqref="D3:Z3">
       <formula1>"double,int,bool,string,float,enum,string[],uint,short,Vector2[],Vector3Int[],int4[],int4,Vector3Int,Vector3,Vector4[],Vector2,Vector4,Color,Color32,Vector2Int,Vector3[],Vector2Int[],Type,long[],bool[],int[],float[],double[],float[][],decimal,double[][]"</formula1>
     </dataValidation>
   </dataValidations>
